--- a/GameTable/Languages/Chinese_Default_Lang.xlsx
+++ b/GameTable/Languages/Chinese_Default_Lang.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -11,8 +11,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -27,33 +27,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
-    <t>id</t>
+    <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t>key</t>
+    <t xml:space="preserve">key</t>
   </si>
   <si>
-    <t>content</t>
+    <t xml:space="preserve">content</t>
   </si>
   <si>
-    <t>int</t>
+    <t xml:space="preserve">int</t>
   </si>
   <si>
-    <t>string</t>
+    <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t>设置a</t>
+    <t xml:space="preserve">设置a</t>
   </si>
   <si>
-    <t>hallo,111,wo</t>
+    <t xml:space="preserve">hallo,111,wo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -76,7 +76,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -84,7 +84,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -525,148 +525,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -748,19 +748,19 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -771,7 +771,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -818,7 +818,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -849,13 +849,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -885,7 +885,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
@@ -905,7 +905,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
@@ -922,16 +922,16 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" table="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
       <tableStyleElement type="firstColumn" dxfId="3"/>
       <tableStyleElement type="lastColumn" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="firstColumnStripe"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -945,8 +945,8 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1208,44 +1208,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="8.42727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="12.9090909090909"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="0" t="s">
         <v>6</v>
       </c>
     </row>
